--- a/Spine_Projects/01_input_data/01_input_raw/Products/methane/Model_Data_Base_methane.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/methane/Model_Data_Base_methane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studentcbs-my.sharepoint.com/personal/djh_eco_cbs_dk/Documents/Documents/GitHub/Nord_H2ub/Spine_Projects/01_input_data/01_input_raw/Products/methane/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\methane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{11E80F7D-C7BD-4A52-82DB-1249CC81A3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F0413D9-E565-4763-B6E0-2FEA282DD39E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF09A765-5BD1-4CE1-AB77-64803296BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="4575" yWindow="4290" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="119">
   <si>
     <t>Unit</t>
   </si>
@@ -404,6 +404,33 @@
   </si>
   <si>
     <t>Relation_In1_Out1</t>
+  </si>
+  <si>
+    <t>pl_wholesale_solar</t>
+  </si>
+  <si>
+    <t>solar_plant_node</t>
+  </si>
+  <si>
+    <t>pl_solar_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_onshore</t>
+  </si>
+  <si>
+    <t>wind_onshore_plant_node</t>
+  </si>
+  <si>
+    <t>pl_wind_onshore_PPA</t>
+  </si>
+  <si>
+    <t>pl_wholesale_wind_offshore</t>
+  </si>
+  <si>
+    <t>wind_offshore_plant_node</t>
+  </si>
+  <si>
+    <t>pl_wind_offshore_PPA</t>
   </si>
 </sst>
 </file>
@@ -425,7 +452,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -438,8 +465,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -467,11 +500,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -482,6 +541,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -932,14 +996,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="18" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -995,7 +1059,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1003,12 +1067,12 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
@@ -1016,12 +1080,12 @@
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -1029,12 +1093,12 @@
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -1056,7 +1120,7 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
@@ -1070,7 +1134,7 @@
       <c r="P6" s="1"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -1084,7 +1148,7 @@
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -1114,14 +1178,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A86F1AE-0A9A-41EF-AAC6-2EFA35CD0F28}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="9.81640625" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="17" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1174,7 +1238,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>76</v>
       </c>
@@ -1182,10 +1246,10 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>85</v>
       </c>
@@ -1193,10 +1257,10 @@
         <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>86</v>
       </c>
@@ -1204,10 +1268,10 @@
         <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -1233,7 +1297,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
@@ -1268,7 +1332,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -1282,7 +1346,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>105</v>
       </c>
@@ -1307,33 +1371,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:Z5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:Z11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.81640625" customWidth="1"/>
-    <col min="19" max="19" width="12.7265625" customWidth="1"/>
-    <col min="20" max="20" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="19.453125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="36.54296875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.85546875" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" customWidth="1"/>
+    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1413,7 +1477,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1472,7 +1536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1528,7 +1592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>67</v>
       </c>
@@ -1554,7 +1618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>68</v>
       </c>
@@ -1589,6 +1653,360 @@
         <v>47</v>
       </c>
       <c r="Z5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="N6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="O6" s="7">
+        <v>1000</v>
+      </c>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7">
+        <v>1</v>
+      </c>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7">
+        <v>1</v>
+      </c>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="4">
+        <v>1000</v>
+      </c>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4">
+        <v>1</v>
+      </c>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="N8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="O8" s="7">
+        <v>1000</v>
+      </c>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7">
+        <v>1</v>
+      </c>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7">
+        <v>1</v>
+      </c>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="4">
+        <v>1000</v>
+      </c>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4">
+        <v>1</v>
+      </c>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z9" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="O10" s="7">
+        <v>1000</v>
+      </c>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7">
+        <v>1</v>
+      </c>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7">
+        <v>1</v>
+      </c>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z10" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4">
+        <v>1000</v>
+      </c>
+      <c r="M11" s="4">
+        <v>1000</v>
+      </c>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4">
+        <v>1</v>
+      </c>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z11" s="10">
         <v>1</v>
       </c>
     </row>
@@ -1604,20 +2022,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" customWidth="1"/>
-    <col min="7" max="7" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1649,7 +2067,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -1675,7 +2093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>63</v>
       </c>
@@ -1712,99 +2130,99 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F682EA3-CCEB-45E2-AC25-979810840C6C}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/methane/Model_Data_Base_methane.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/methane/Model_Data_Base_methane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\methane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF09A765-5BD1-4CE1-AB77-64803296BCDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0833C1-9E75-49D3-92ED-B22530030FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4575" yWindow="4290" windowWidth="38700" windowHeight="15345" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="120">
   <si>
     <t>Unit</t>
   </si>
@@ -325,9 +325,6 @@
     <t>Auxilliary</t>
   </si>
   <si>
-    <t>heat_low</t>
-  </si>
-  <si>
     <t>Auxiliary</t>
   </si>
   <si>
@@ -431,6 +428,12 @@
   </si>
   <si>
     <t>pl_wind_offshore_PPA</t>
+  </si>
+  <si>
+    <t>excess_heat</t>
+  </si>
+  <si>
+    <t>heat</t>
   </si>
 </sst>
 </file>
@@ -998,9 +1001,24 @@
   <dimension ref="A1:R8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1011,7 +1029,7 @@
         <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D1" t="s">
         <v>34</v>
@@ -1020,16 +1038,16 @@
         <v>31</v>
       </c>
       <c r="F1" t="s">
+        <v>99</v>
+      </c>
+      <c r="G1" t="s">
         <v>100</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>101</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>102</v>
-      </c>
-      <c r="I1" t="s">
-        <v>103</v>
       </c>
       <c r="J1" t="s">
         <v>79</v>
@@ -1047,7 +1065,7 @@
         <v>25</v>
       </c>
       <c r="O1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P1" t="s">
         <v>36</v>
@@ -1067,33 +1085,33 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
@@ -1125,7 +1143,7 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>70</v>
@@ -1136,7 +1154,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
         <v>82</v>
@@ -1150,13 +1168,13 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s">
         <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1180,9 +1198,16 @@
   <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="17" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1199,10 +1224,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" t="s">
         <v>93</v>
-      </c>
-      <c r="F1" t="s">
-        <v>94</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -1211,31 +1236,31 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
         <v>89</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1" t="s">
+        <v>91</v>
+      </c>
+      <c r="N1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O1" t="s">
         <v>95</v>
       </c>
-      <c r="K1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" t="s">
-        <v>109</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>96</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>97</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -1246,29 +1271,29 @@
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -1288,7 +1313,7 @@
         <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="K5">
         <v>5.8500000000000002E-3</v>
@@ -1308,7 +1333,7 @@
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>74</v>
@@ -1317,7 +1342,7 @@
         <v>70</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="K6">
         <v>0.86792452830188682</v>
@@ -1334,13 +1359,13 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B7" t="s">
         <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" t="s">
         <v>78</v>
@@ -1348,16 +1373,16 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B8" t="s">
         <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -1374,27 +1399,28 @@
   <dimension ref="A1:Z11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="35.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.85546875" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" x14ac:dyDescent="0.25">
@@ -1626,7 +1652,7 @@
         <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
         <v>69</v>
@@ -1658,7 +1684,7 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>45</v>
@@ -1667,10 +1693,10 @@
         <v>71</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>71</v>
@@ -1724,13 +1750,13 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
@@ -1776,7 +1802,7 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>45</v>
@@ -1785,10 +1811,10 @@
         <v>71</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>71</v>
@@ -1842,13 +1868,13 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
@@ -1894,7 +1920,7 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>45</v>
@@ -1903,10 +1929,10 @@
         <v>71</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>71</v>
@@ -1960,13 +1986,13 @@
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4" t="s">
@@ -2024,15 +2050,16 @@
   <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -2131,6 +2158,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F682EA3-CCEB-45E2-AC25-979810840C6C}">
   <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -2224,7 +2254,7 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Spine_Projects/01_input_data/01_input_raw/Products/methane/Model_Data_Base_methane.xlsx
+++ b/Spine_Projects/01_input_data/01_input_raw/Products/methane/Model_Data_Base_methane.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kar.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\methane\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\Nord_H2ub\Spine_Projects\01_input_data\01_input_raw\Products\methane\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0833C1-9E75-49D3-92ED-B22530030FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737619C0-585A-4C90-9994-68E129893313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
+    <workbookView xWindow="-10110" yWindow="-21720" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{50334894-9481-4F8E-BD29-206032E10C62}"/>
   </bookViews>
   <sheets>
     <sheet name="Units" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentManualCount="6"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="117">
   <si>
     <t>Unit</t>
   </si>
@@ -280,12 +280,6 @@
     <t>pl_ch4_st</t>
   </si>
   <si>
-    <t>pl_dh</t>
-  </si>
-  <si>
-    <t>dh</t>
-  </si>
-  <si>
     <t>ch4</t>
   </si>
   <si>
@@ -431,9 +425,6 @@
   </si>
   <si>
     <t>excess_heat</t>
-  </si>
-  <si>
-    <t>heat</t>
   </si>
 </sst>
 </file>
@@ -558,18 +549,18 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -603,8 +594,8 @@
     <tableColumn id="13" xr3:uid="{AD4231E3-CB94-4597-81A2-E13C044BBD2D}" name="fom_cost"/>
     <tableColumn id="22" xr3:uid="{3FA572AD-B473-45F7-A244-2DF38E57A2D3}" name="vom_cost"/>
     <tableColumn id="36" xr3:uid="{CFFB3FD3-3581-4635-8E26-A397976C50BA}" name="minimum_op_point"/>
-    <tableColumn id="40" xr3:uid="{13D3F1BD-DB2E-4B88-B660-2F6A81616F69}" name="resolution_output" dataDxfId="3"/>
-    <tableColumn id="41" xr3:uid="{8CF0CBE3-C92A-4542-8737-317CCD5CF213}" name="demand" dataDxfId="2"/>
+    <tableColumn id="40" xr3:uid="{13D3F1BD-DB2E-4B88-B660-2F6A81616F69}" name="resolution_output" dataDxfId="2"/>
+    <tableColumn id="41" xr3:uid="{8CF0CBE3-C92A-4542-8737-317CCD5CF213}" name="demand" dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{67AC62F1-20D0-460D-AB19-8D9D0208B920}" name="initial_units_on"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -638,15 +629,15 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:Z5" totalsRowShown="0">
-  <autoFilter ref="A1:Z5" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{856854C3-DC05-4AB8-91B8-0E52D9C11DBC}" name="Table13" displayName="Table13" ref="A1:Z4" totalsRowShown="0">
+  <autoFilter ref="A1:Z4" xr:uid="{A55D93BB-3EF1-4249-80C0-A8E75E738393}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{26B0CA71-1EA9-44CF-8E6D-31054ECA99A6}" name="Connection"/>
     <tableColumn id="2" xr3:uid="{587ADBB8-7B68-42BE-A14F-535C6116E5EA}" name="Object_type"/>
     <tableColumn id="3" xr3:uid="{0B221EED-10BC-4C34-AC5E-37A826B1E8AE}" name="Input1"/>
     <tableColumn id="4" xr3:uid="{13095F0A-BCF6-40A3-B029-60B11214B154}" name="Input2"/>
     <tableColumn id="5" xr3:uid="{4C6B3E52-C4A2-4D67-B50B-9DAA089E0399}" name="Output1"/>
-    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Output2" dataDxfId="1"/>
+    <tableColumn id="22" xr3:uid="{551A8663-4680-4147-9E64-4B9A8EA76642}" name="Output2" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{5DF4D35D-AD4C-4648-BC90-B2BA8F975A09}" name="Connection_type"/>
     <tableColumn id="15" xr3:uid="{C0BCA9EF-0E20-40E5-9820-0EA6AB1DE457}" name="Cap_Input1_existing"/>
     <tableColumn id="14" xr3:uid="{D4F16D16-99DE-47DA-B08A-6DD56FEBC7A4}" name="Cap_Input1_max"/>
@@ -999,29 +990,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576C757C-091A-46DF-949E-B17661031FDE}">
   <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +1020,7 @@
         <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D1" t="s">
         <v>34</v>
@@ -1038,22 +1029,22 @@
         <v>31</v>
       </c>
       <c r="F1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" t="s">
         <v>99</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>100</v>
       </c>
-      <c r="H1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I1" t="s">
-        <v>102</v>
-      </c>
       <c r="J1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L1" t="s">
         <v>35</v>
@@ -1065,7 +1056,7 @@
         <v>25</v>
       </c>
       <c r="O1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="P1" t="s">
         <v>36</v>
@@ -1074,57 +1065,57 @@
         <v>37</v>
       </c>
       <c r="R1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5">
         <v>0.75</v>
@@ -1138,43 +1129,43 @@
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="N6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="2"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N7" s="5"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
@@ -1196,21 +1187,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A86F1AE-0A9A-41EF-AAC6-2EFA35CD0F28}">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1224,10 +1215,10 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
@@ -1236,84 +1227,84 @@
         <v>4</v>
       </c>
       <c r="I1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" t="s">
+        <v>87</v>
+      </c>
+      <c r="L1" t="s">
         <v>88</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
+        <v>89</v>
+      </c>
+      <c r="N1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O1" t="s">
+        <v>93</v>
+      </c>
+      <c r="P1" t="s">
         <v>94</v>
       </c>
-      <c r="K1" t="s">
-        <v>89</v>
-      </c>
-      <c r="L1" t="s">
-        <v>90</v>
-      </c>
-      <c r="M1" t="s">
-        <v>91</v>
-      </c>
-      <c r="N1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>95</v>
       </c>
-      <c r="P1" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
         <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
       <c r="G3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
         <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
         <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K5">
         <v>5.8500000000000002E-3</v>
@@ -1322,7 +1313,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>43</v>
       </c>
@@ -1330,19 +1321,19 @@
         <v>61</v>
       </c>
       <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
         <v>72</v>
       </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" t="s">
-        <v>74</v>
-      </c>
       <c r="G6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="K6">
         <v>0.86792452830188682</v>
@@ -1357,32 +1348,32 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" t="s">
         <v>104</v>
       </c>
-      <c r="B8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" t="s">
-        <v>106</v>
-      </c>
       <c r="G8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -1396,34 +1387,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C870BDA0-9E4C-481D-87BE-9D47789809C8}">
-  <dimension ref="A1:Z11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="25.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="38.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="38.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="38.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1500,10 +1491,10 @@
         <v>33</v>
       </c>
       <c r="Z1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>65</v>
       </c>
@@ -1511,16 +1502,16 @@
         <v>45</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
         <v>46</v>
@@ -1562,7 +1553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>66</v>
       </c>
@@ -1570,16 +1561,16 @@
         <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
         <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
         <v>49</v>
@@ -1618,7 +1609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>67</v>
       </c>
@@ -1626,13 +1617,13 @@
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
         <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
         <v>63</v>
@@ -1640,399 +1631,388 @@
       <c r="G4" t="s">
         <v>49</v>
       </c>
+      <c r="H4">
+        <v>1000</v>
+      </c>
+      <c r="J4">
+        <v>1000</v>
+      </c>
+      <c r="K4">
+        <v>1000</v>
+      </c>
+      <c r="L4">
+        <v>1000</v>
+      </c>
+      <c r="M4">
+        <v>1000</v>
+      </c>
+      <c r="N4">
+        <v>1000</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>50</v>
+      </c>
       <c r="Z4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="G5" t="s">
+      <c r="D5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H5">
-        <v>1000</v>
-      </c>
-      <c r="I5">
-        <v>1000</v>
-      </c>
-      <c r="L5">
-        <v>1000</v>
-      </c>
-      <c r="M5">
-        <v>1000</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-      <c r="Y5" t="s">
+      <c r="H5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="M5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="N5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="O5" s="7">
+        <v>1000</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7">
+        <v>1</v>
+      </c>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7">
+        <v>1</v>
+      </c>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="Z5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+      <c r="Z5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="7" t="s">
+      <c r="C6" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="M6" s="4">
+        <v>1000</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4">
+        <v>1</v>
+      </c>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="B7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="J6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="L6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="M6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="N6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="O6" s="7">
-        <v>1000</v>
-      </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="7">
-        <v>1</v>
-      </c>
-      <c r="S6" s="7"/>
-      <c r="T6" s="7">
-        <v>1</v>
-      </c>
-      <c r="U6" s="7"/>
-      <c r="V6" s="7"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
-      <c r="Y6" s="7" t="s">
+      <c r="H7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="N7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="O7" s="7">
+        <v>1000</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7">
+        <v>1</v>
+      </c>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7">
+        <v>1</v>
+      </c>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="Z7" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A8" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="M8" s="4">
+        <v>1000</v>
+      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="C9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="H7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="M7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4">
-        <v>1</v>
-      </c>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="4"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4" t="s">
+      <c r="H9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="I9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="J9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="K9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="L9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="M9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="N9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="O9" s="7">
+        <v>1000</v>
+      </c>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7">
+        <v>1</v>
+      </c>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7">
+        <v>1</v>
+      </c>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="Z7" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="Z9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="7" t="s">
+      <c r="C10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="I8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="J8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="L8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="M8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="N8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="O8" s="7">
-        <v>1000</v>
-      </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="7">
-        <v>1</v>
-      </c>
-      <c r="S8" s="7"/>
-      <c r="T8" s="7">
-        <v>1</v>
-      </c>
-      <c r="U8" s="7"/>
-      <c r="V8" s="7"/>
-      <c r="W8" s="7"/>
-      <c r="X8" s="7"/>
-      <c r="Y8" s="7" t="s">
+      <c r="H10" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1000</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4">
+        <v>1000</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1000</v>
+      </c>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4">
+        <v>1</v>
+      </c>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="Z8" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="4">
-        <v>1000</v>
-      </c>
-      <c r="I9" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4">
-        <v>1000</v>
-      </c>
-      <c r="M9" s="4">
-        <v>1000</v>
-      </c>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4">
-        <v>1</v>
-      </c>
-      <c r="U9" s="4"/>
-      <c r="V9" s="4"/>
-      <c r="W9" s="4"/>
-      <c r="X9" s="4"/>
-      <c r="Y9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z9" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="I10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="J10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="K10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="L10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="M10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="N10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="O10" s="7">
-        <v>1000</v>
-      </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7">
-        <v>1</v>
-      </c>
-      <c r="S10" s="7"/>
-      <c r="T10" s="7">
-        <v>1</v>
-      </c>
-      <c r="U10" s="7"/>
-      <c r="V10" s="7"/>
-      <c r="W10" s="7"/>
-      <c r="X10" s="7"/>
-      <c r="Y10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z10" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="4">
-        <v>1000</v>
-      </c>
-      <c r="I11" s="4">
-        <v>1000</v>
-      </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4">
-        <v>1000</v>
-      </c>
-      <c r="M11" s="4">
-        <v>1000</v>
-      </c>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4">
-        <v>1</v>
-      </c>
-      <c r="U11" s="4"/>
-      <c r="V11" s="4"/>
-      <c r="W11" s="4"/>
-      <c r="X11" s="4"/>
-      <c r="Y11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z11" s="10">
+      <c r="Z10" s="10">
         <v>1</v>
       </c>
     </row>
@@ -2048,21 +2028,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981CFA5E-60F3-446F-A856-2FA65B76879A}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -2094,7 +2074,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>62</v>
       </c>
@@ -2120,7 +2100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>63</v>
       </c>
@@ -2157,104 +2137,104 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F682EA3-CCEB-45E2-AC25-979810840C6C}">
   <dimension ref="A1:A19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
